--- a/data/trans_orig/P41E_2023_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en el último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023</t>
+          <t>Población que en el último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57073</t>
+          <t>57230</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81500</t>
+          <t>79547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83464</t>
+          <t>84545</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>108062</t>
+          <t>106919</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148611</t>
+          <t>148141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182282</t>
+          <t>180937</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>157342</t>
+          <t>159295</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>181769</t>
+          <t>181612</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166214</t>
+          <t>167357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>190812</t>
+          <t>189731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>330836</t>
+          <t>332181</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>364507</t>
+          <t>364977</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,13%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46873</t>
+          <t>41197</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>122161</t>
+          <t>121227</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>40551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96656</t>
+          <t>97032</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112739</t>
+          <t>110397</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207106</t>
+          <t>205944</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1050173</t>
+          <t>1051107</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1125461</t>
+          <t>1131137</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>975503</t>
+          <t>975127</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1032680</t>
+          <t>1031608</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2037387</t>
+          <t>2038549</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2131754</t>
+          <t>2134096</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22863</t>
+          <t>23368</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21747</t>
+          <t>22212</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22386</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40615</t>
+          <t>39934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>323920</t>
+          <t>323415</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>336599</t>
+          <t>336720</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>298024</t>
+          <t>297559</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>309782</t>
+          <t>309739</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>625939</t>
+          <t>626620</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644168</t>
+          <t>643616</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108810</t>
+          <t>108972</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>210534</t>
+          <t>212476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116250</t>
+          <t>124717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>215928</t>
+          <t>218387</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>266177</t>
+          <t>271515</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>413061</t>
+          <t>412870</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1547424</t>
+          <t>1545482</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1649148</t>
+          <t>1648986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1450279</t>
+          <t>1447820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1549957</t>
+          <t>1541490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3011104</t>
+          <t>3011295</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3157988</t>
+          <t>3152650</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41E_2023_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023_R-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>68179</t>
+          <t>73838</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57230</t>
+          <t>61866</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79547</t>
+          <t>87562</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>95109</t>
+          <t>105047</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84545</t>
+          <t>92531</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106919</t>
+          <t>118085</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>163288</t>
+          <t>178885</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148141</t>
+          <t>162291</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180937</t>
+          <t>199096</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>170663</t>
+          <t>190865</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>159295</t>
+          <t>177141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>181612</t>
+          <t>202837</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>179167</t>
+          <t>194899</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>167357</t>
+          <t>181861</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>189731</t>
+          <t>207415</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>349830</t>
+          <t>385764</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>332181</t>
+          <t>365553</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>364977</t>
+          <t>402358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,26%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>238842</t>
+          <t>264703</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>238842</t>
+          <t>264703</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>238842</t>
+          <t>264703</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>274276</t>
+          <t>299946</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>274276</t>
+          <t>299946</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>274276</t>
+          <t>299946</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>513118</t>
+          <t>564649</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>513118</t>
+          <t>564649</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>513118</t>
+          <t>564649</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90656</t>
+          <t>95776</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41197</t>
+          <t>77763</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121227</t>
+          <t>113574</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>72564</t>
+          <t>79075</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40551</t>
+          <t>67046</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97032</t>
+          <t>94559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>163220</t>
+          <t>174851</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110397</t>
+          <t>151288</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205944</t>
+          <t>195633</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1081678</t>
+          <t>914355</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1051107</t>
+          <t>896557</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1131137</t>
+          <t>932368</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>999595</t>
+          <t>878920</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>975127</t>
+          <t>863436</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1031608</t>
+          <t>890949</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2081273</t>
+          <t>1793275</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2038549</t>
+          <t>1772493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2134096</t>
+          <t>1816838</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1172334</t>
+          <t>1010131</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1172334</t>
+          <t>1010131</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1172334</t>
+          <t>1010131</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1072159</t>
+          <t>957995</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1072159</t>
+          <t>957995</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1072159</t>
+          <t>957995</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2244493</t>
+          <t>1968126</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2244493</t>
+          <t>1968126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2244493</t>
+          <t>1968126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15536</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>11133</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23368</t>
+          <t>24786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15017</t>
+          <t>16049</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10032</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>22940</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>30553</t>
+          <t>32861</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22938</t>
+          <t>23786</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39934</t>
+          <t>42506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>331247</t>
+          <t>366424</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>323415</t>
+          <t>358450</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>336720</t>
+          <t>372103</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>304754</t>
+          <t>342846</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>297559</t>
+          <t>335955</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>309739</t>
+          <t>348548</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>636001</t>
+          <t>709270</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>626620</t>
+          <t>699625</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>643616</t>
+          <t>718345</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>346783</t>
+          <t>383236</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>346783</t>
+          <t>383236</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>346783</t>
+          <t>383236</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>319771</t>
+          <t>358895</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>319771</t>
+          <t>358895</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>319771</t>
+          <t>358895</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>666554</t>
+          <t>742131</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>666554</t>
+          <t>742131</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>666554</t>
+          <t>742131</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>174371</t>
+          <t>186426</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108972</t>
+          <t>164551</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>212476</t>
+          <t>209289</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>11,24%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>9,92%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>182690</t>
+          <t>200171</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124717</t>
+          <t>179024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>218387</t>
+          <t>221068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>357061</t>
+          <t>386597</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>271515</t>
+          <t>356316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>412870</t>
+          <t>420388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -1867,34 +1867,34 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1583587</t>
+          <t>1471645</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1545482</t>
+          <t>1448782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1648986</t>
+          <t>1493520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>88,76%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>90,08%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,8%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>2069</t>
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1483517</t>
+          <t>1416664</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1447820</t>
+          <t>1395767</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1541490</t>
+          <t>1437811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3067104</t>
+          <t>2888309</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3011295</t>
+          <t>2854518</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3152650</t>
+          <t>2918590</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1757958</t>
+          <t>1658071</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1757958</t>
+          <t>1658071</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1757958</t>
+          <t>1658071</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1666207</t>
+          <t>1616835</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1666207</t>
+          <t>1616835</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1666207</t>
+          <t>1616835</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3424165</t>
+          <t>3274906</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3424165</t>
+          <t>3274906</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3424165</t>
+          <t>3274906</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P41E_2023_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en el último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
+          <t>Población que en el último año declara que sus relaciones sexuales no han sido satisfactorias para ambas partes (bastante en desacuerdo/totalmente en desacuerdo) en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
